--- a/models/demo-species/demo-species.xlsx
+++ b/models/demo-species/demo-species.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shxie/Projects/anse-models/demo-species/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shxie/projects/anse-models/demo-species/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96355D77-A691-254A-BEC0-1D45BEB6D9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3B2365E-4C6E-444F-96F7-DABD6FD8521D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="600" windowWidth="25600" windowHeight="26900" xr2:uid="{73351A0E-E394-C94F-8AB9-3EA9DA143F24}"/>
+    <workbookView xWindow="25600" yWindow="600" windowWidth="25600" windowHeight="26900" activeTab="2" xr2:uid="{73351A0E-E394-C94F-8AB9-3EA9DA143F24}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs - Flow Network" sheetId="1" r:id="rId1"/>
@@ -413,7 +413,7 @@
     <author>Magnan, Michael</author>
   </authors>
   <commentList>
-    <comment ref="B26" authorId="0" shapeId="0" xr:uid="{CC7F5D1D-B34F-1646-BA4F-A18CC3CBED25}">
+    <comment ref="B43" authorId="0" shapeId="0" xr:uid="{CC7F5D1D-B34F-1646-BA4F-A18CC3CBED25}">
       <text>
         <r>
           <rPr>
@@ -645,7 +645,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="133">
   <si>
     <t>Keyword: POOL</t>
   </si>
@@ -974,21 +974,9 @@
     <t>Roundwood</t>
   </si>
   <si>
-    <t>Sawnwood</t>
-  </si>
-  <si>
-    <t>Panels</t>
-  </si>
-  <si>
-    <t>Paper</t>
-  </si>
-  <si>
     <t>SPECIES</t>
   </si>
   <si>
-    <t>Bioenergy</t>
-  </si>
-  <si>
     <t>ACTION_TYPE</t>
   </si>
   <si>
@@ -1017,6 +1005,45 @@
   </si>
   <si>
     <t>Hem-Fir</t>
+  </si>
+  <si>
+    <t>SPECIES_GROUP</t>
+  </si>
+  <si>
+    <t>Spruce</t>
+  </si>
+  <si>
+    <t>Pine</t>
+  </si>
+  <si>
+    <t>Fir</t>
+  </si>
+  <si>
+    <t>Hemlock</t>
+  </si>
+  <si>
+    <t>Douglas-fir</t>
+  </si>
+  <si>
+    <t>Larch</t>
+  </si>
+  <si>
+    <t>SPECIES_GROUP_MEMBER</t>
+  </si>
+  <si>
+    <t>Hardwood</t>
+  </si>
+  <si>
+    <t>&gt; 8"</t>
+  </si>
+  <si>
+    <t>6-8"</t>
+  </si>
+  <si>
+    <t>&lt; 6" clean</t>
+  </si>
+  <si>
+    <t>&lt; 2" or contaminated</t>
   </si>
 </sst>
 </file>
@@ -1682,26 +1709,26 @@
     </row>
     <row r="20" spans="2:7" ht="16" customHeight="1">
       <c r="B20" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C20" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="16" customHeight="1">
       <c r="B21" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C21" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="16" customHeight="1">
       <c r="B22" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C22" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="2:7" s="3" customFormat="1" ht="16" customHeight="1">
@@ -2053,10 +2080,10 @@
       </c>
       <c r="G49" t="str">
         <f>'Inputs - Categorical'!$C$4</f>
-        <v>Sawnwood</v>
+        <v>&gt; 8"</v>
       </c>
       <c r="I49" t="str">
-        <f>'Inputs - Categorical'!$C$15</f>
+        <f>'Inputs - Categorical'!$C$25</f>
         <v>SPF</v>
       </c>
     </row>
@@ -2077,10 +2104,10 @@
       </c>
       <c r="G50" t="str">
         <f>'Inputs - Categorical'!$C$5</f>
-        <v>Panels</v>
+        <v>6-8"</v>
       </c>
       <c r="I50" t="str">
-        <f>'Inputs - Categorical'!$C$15</f>
+        <f>'Inputs - Categorical'!$C$25</f>
         <v>SPF</v>
       </c>
     </row>
@@ -2101,10 +2128,10 @@
       </c>
       <c r="G51" t="str">
         <f>'Inputs - Categorical'!$C$6</f>
-        <v>Paper</v>
+        <v>&lt; 6" clean</v>
       </c>
       <c r="I51" t="str">
-        <f>'Inputs - Categorical'!$C$15</f>
+        <f>'Inputs - Categorical'!$C$25</f>
         <v>SPF</v>
       </c>
     </row>
@@ -2125,10 +2152,10 @@
       </c>
       <c r="G52" t="str">
         <f>'Inputs - Categorical'!$C$7</f>
-        <v>Bioenergy</v>
+        <v>&lt; 2" or contaminated</v>
       </c>
       <c r="I52" t="str">
-        <f>'Inputs - Categorical'!$C$15</f>
+        <f>'Inputs - Categorical'!$C$25</f>
         <v>SPF</v>
       </c>
     </row>
@@ -2149,11 +2176,11 @@
       </c>
       <c r="G54" t="str">
         <f>'Inputs - Categorical'!$C$4</f>
-        <v>Sawnwood</v>
+        <v>&gt; 8"</v>
       </c>
       <c r="I54" t="str">
-        <f>'Inputs - Categorical'!$C$16</f>
-        <v>Aspen</v>
+        <f>'Inputs - Categorical'!$C$26</f>
+        <v>Hardwood</v>
       </c>
     </row>
     <row r="55" spans="2:9" ht="16" customHeight="1">
@@ -2173,11 +2200,11 @@
       </c>
       <c r="G55" t="str">
         <f>'Inputs - Categorical'!$C$5</f>
-        <v>Panels</v>
+        <v>6-8"</v>
       </c>
       <c r="I55" t="str">
-        <f>'Inputs - Categorical'!$C$16</f>
-        <v>Aspen</v>
+        <f>'Inputs - Categorical'!$C$26</f>
+        <v>Hardwood</v>
       </c>
     </row>
     <row r="56" spans="2:9" ht="16" customHeight="1">
@@ -2197,11 +2224,11 @@
       </c>
       <c r="G56" t="str">
         <f>'Inputs - Categorical'!$C$6</f>
-        <v>Paper</v>
+        <v>&lt; 6" clean</v>
       </c>
       <c r="I56" t="str">
-        <f>'Inputs - Categorical'!$C$16</f>
-        <v>Aspen</v>
+        <f>'Inputs - Categorical'!$C$26</f>
+        <v>Hardwood</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="16" customHeight="1">
@@ -2221,11 +2248,11 @@
       </c>
       <c r="G57" t="str">
         <f>'Inputs - Categorical'!$C$7</f>
-        <v>Bioenergy</v>
+        <v>&lt; 2" or contaminated</v>
       </c>
       <c r="I57" t="str">
-        <f>'Inputs - Categorical'!$C$16</f>
-        <v>Aspen</v>
+        <f>'Inputs - Categorical'!$C$26</f>
+        <v>Hardwood</v>
       </c>
     </row>
     <row r="59" spans="2:9" ht="16" customHeight="1">
@@ -2245,10 +2272,10 @@
       </c>
       <c r="G59" t="str">
         <f>'Inputs - Categorical'!$C$4</f>
-        <v>Sawnwood</v>
+        <v>&gt; 8"</v>
       </c>
       <c r="I59" t="str">
-        <f>'Inputs - Categorical'!$C$17</f>
+        <f>'Inputs - Categorical'!$C$27</f>
         <v>Hem-Fir</v>
       </c>
     </row>
@@ -2269,10 +2296,10 @@
       </c>
       <c r="G60" t="str">
         <f>'Inputs - Categorical'!$C$5</f>
-        <v>Panels</v>
+        <v>6-8"</v>
       </c>
       <c r="I60" t="str">
-        <f>'Inputs - Categorical'!$C$17</f>
+        <f>'Inputs - Categorical'!$C$27</f>
         <v>Hem-Fir</v>
       </c>
     </row>
@@ -2293,10 +2320,10 @@
       </c>
       <c r="G61" t="str">
         <f>'Inputs - Categorical'!$C$6</f>
-        <v>Paper</v>
+        <v>&lt; 6" clean</v>
       </c>
       <c r="I61" t="str">
-        <f>'Inputs - Categorical'!$C$17</f>
+        <f>'Inputs - Categorical'!$C$27</f>
         <v>Hem-Fir</v>
       </c>
     </row>
@@ -2317,10 +2344,10 @@
       </c>
       <c r="G62" t="str">
         <f>'Inputs - Categorical'!$C$7</f>
-        <v>Bioenergy</v>
+        <v>&lt; 2" or contaminated</v>
       </c>
       <c r="I62" t="str">
-        <f>'Inputs - Categorical'!$C$17</f>
+        <f>'Inputs - Categorical'!$C$27</f>
         <v>Hem-Fir</v>
       </c>
     </row>
@@ -2341,10 +2368,10 @@
       </c>
       <c r="G64" t="str">
         <f>'Inputs - Categorical'!C4</f>
-        <v>Sawnwood</v>
+        <v>&gt; 8"</v>
       </c>
       <c r="I64" t="str">
-        <f>'Inputs - Categorical'!$C$18</f>
+        <f>'Inputs - Categorical'!$C$28</f>
         <v>DFL</v>
       </c>
     </row>
@@ -2365,10 +2392,10 @@
       </c>
       <c r="G65" t="str">
         <f>'Inputs - Categorical'!C5</f>
-        <v>Panels</v>
+        <v>6-8"</v>
       </c>
       <c r="I65" t="str">
-        <f>'Inputs - Categorical'!$C$18</f>
+        <f>'Inputs - Categorical'!$C$28</f>
         <v>DFL</v>
       </c>
     </row>
@@ -2389,10 +2416,10 @@
       </c>
       <c r="G66" t="str">
         <f>'Inputs - Categorical'!C6</f>
-        <v>Paper</v>
+        <v>&lt; 6" clean</v>
       </c>
       <c r="I66" t="str">
-        <f>'Inputs - Categorical'!$C$18</f>
+        <f>'Inputs - Categorical'!$C$28</f>
         <v>DFL</v>
       </c>
     </row>
@@ -2413,10 +2440,10 @@
       </c>
       <c r="G67" t="str">
         <f>'Inputs - Categorical'!C7</f>
-        <v>Bioenergy</v>
+        <v>&lt; 2" or contaminated</v>
       </c>
       <c r="I67" t="str">
-        <f>'Inputs - Categorical'!$C$18</f>
+        <f>'Inputs - Categorical'!$C$28</f>
         <v>DFL</v>
       </c>
     </row>
@@ -2429,7 +2456,7 @@
         <v>Commodity Demand, CAT</v>
       </c>
       <c r="D69">
-        <f t="shared" ref="D69:D72" si="6">F28</f>
+        <f>F28</f>
         <v>1</v>
       </c>
       <c r="E69">
@@ -2437,7 +2464,7 @@
       </c>
       <c r="G69" t="str">
         <f>'Inputs - Categorical'!C4</f>
-        <v>Sawnwood</v>
+        <v>&gt; 8"</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="16" customHeight="1">
@@ -2445,11 +2472,11 @@
         <v>45</v>
       </c>
       <c r="C70" t="str">
-        <f t="shared" ref="C70:C72" si="7">$C$43</f>
+        <f t="shared" ref="C70:C72" si="6">$C$43</f>
         <v>Commodity Demand, CAT</v>
       </c>
       <c r="D70">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="D70:D72" si="7">F29</f>
         <v>2</v>
       </c>
       <c r="E70">
@@ -2457,7 +2484,7 @@
       </c>
       <c r="G70" t="str">
         <f>'Inputs - Categorical'!C5</f>
-        <v>Panels</v>
+        <v>6-8"</v>
       </c>
     </row>
     <row r="71" spans="2:9" ht="16" customHeight="1">
@@ -2465,11 +2492,11 @@
         <v>45</v>
       </c>
       <c r="C71" t="str">
+        <f t="shared" si="6"/>
+        <v>Commodity Demand, CAT</v>
+      </c>
+      <c r="D71">
         <f t="shared" si="7"/>
-        <v>Commodity Demand, CAT</v>
-      </c>
-      <c r="D71">
-        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="E71">
@@ -2477,7 +2504,7 @@
       </c>
       <c r="G71" t="str">
         <f>'Inputs - Categorical'!C6</f>
-        <v>Paper</v>
+        <v>&lt; 6" clean</v>
       </c>
     </row>
     <row r="72" spans="2:9" ht="16" customHeight="1">
@@ -2485,11 +2512,11 @@
         <v>45</v>
       </c>
       <c r="C72" t="str">
+        <f t="shared" si="6"/>
+        <v>Commodity Demand, CAT</v>
+      </c>
+      <c r="D72">
         <f t="shared" si="7"/>
-        <v>Commodity Demand, CAT</v>
-      </c>
-      <c r="D72">
-        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="E72">
@@ -2497,7 +2524,7 @@
       </c>
       <c r="G72" t="str">
         <f>'Inputs - Categorical'!C7</f>
-        <v>Bioenergy</v>
+        <v>&lt; 2" or contaminated</v>
       </c>
     </row>
     <row r="74" spans="2:9" ht="16" customHeight="1">
@@ -2539,7 +2566,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22152807-D21A-1A49-9C05-E8FAC8B5CEA8}">
-  <dimension ref="B1:K5"/>
+  <dimension ref="B1:K8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
@@ -2594,7 +2621,7 @@
       </c>
       <c r="D2" t="str">
         <f>'Inputs - Categorical'!C15</f>
-        <v>SPF</v>
+        <v>Spruce</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -2616,7 +2643,7 @@
       </c>
       <c r="D3" t="str">
         <f>'Inputs - Categorical'!C16</f>
-        <v>Aspen</v>
+        <v>Pine</v>
       </c>
       <c r="F3">
         <v>100</v>
@@ -2638,7 +2665,7 @@
       </c>
       <c r="D4" t="str">
         <f>'Inputs - Categorical'!C17</f>
-        <v>Hem-Fir</v>
+        <v>Fir</v>
       </c>
       <c r="F4">
         <v>100</v>
@@ -2660,7 +2687,7 @@
       </c>
       <c r="D5" t="str">
         <f>'Inputs - Categorical'!C18</f>
-        <v>DFL</v>
+        <v>Hemlock</v>
       </c>
       <c r="F5">
         <v>100</v>
@@ -2669,6 +2696,72 @@
         <v>1</v>
       </c>
       <c r="K5">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11">
+      <c r="B6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" t="str">
+        <f>'Inputs - Flow Network'!$C$3</f>
+        <v>Roundwood, CAT</v>
+      </c>
+      <c r="D6" t="str">
+        <f>'Inputs - Categorical'!C19</f>
+        <v>Douglas-fir</v>
+      </c>
+      <c r="F6">
+        <v>100</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11">
+      <c r="B7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" t="str">
+        <f>'Inputs - Flow Network'!$C$3</f>
+        <v>Roundwood, CAT</v>
+      </c>
+      <c r="D7" t="str">
+        <f>'Inputs - Categorical'!C20</f>
+        <v>Larch</v>
+      </c>
+      <c r="F7">
+        <v>100</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11">
+      <c r="B8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" t="str">
+        <f>'Inputs - Flow Network'!$C$3</f>
+        <v>Roundwood, CAT</v>
+      </c>
+      <c r="D8" t="str">
+        <f>'Inputs - Categorical'!C21</f>
+        <v>Aspen</v>
+      </c>
+      <c r="F8">
+        <v>100</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="K8">
         <v>1990</v>
       </c>
     </row>
@@ -2680,7 +2773,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{990EC481-AC22-9A46-B3DF-F781248D750D}">
-  <dimension ref="B1:G26"/>
+  <dimension ref="B1:G43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -2716,7 +2809,7 @@
         <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="2:7">
@@ -2724,7 +2817,7 @@
         <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="2:7">
@@ -2732,7 +2825,7 @@
         <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="2:7">
@@ -2740,7 +2833,7 @@
         <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="2:7" s="3" customFormat="1">
@@ -2790,72 +2883,219 @@
     </row>
     <row r="15" spans="2:7">
       <c r="B15" t="s">
-        <v>112</v>
-      </c>
-      <c r="C15" t="s">
-        <v>120</v>
+        <v>109</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="2:7">
       <c r="B16" t="s">
-        <v>112</v>
-      </c>
-      <c r="C16" t="s">
-        <v>121</v>
+        <v>109</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="2:5">
       <c r="B17" t="s">
-        <v>112</v>
-      </c>
-      <c r="C17" t="s">
+        <v>109</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="18" spans="2:5">
       <c r="B18" t="s">
-        <v>112</v>
-      </c>
-      <c r="C18" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" s="3" customFormat="1">
-      <c r="B20" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>34</v>
+        <v>109</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5">
+      <c r="B19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5">
+      <c r="B20" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5">
+      <c r="B21" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="23" spans="2:5" s="3" customFormat="1">
       <c r="B23" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5">
+      <c r="B25" t="s">
+        <v>120</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5">
+      <c r="B26" t="s">
+        <v>120</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5">
+      <c r="B27" t="s">
+        <v>120</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5">
+      <c r="B28" t="s">
+        <v>120</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" s="3" customFormat="1">
+      <c r="B30" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C30" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="2:5" s="3" customFormat="1">
-      <c r="B26" s="2" t="s">
+    <row r="32" spans="2:5">
+      <c r="B32" t="s">
+        <v>127</v>
+      </c>
+      <c r="C32" t="str">
+        <f>$C$25</f>
+        <v>SPF</v>
+      </c>
+      <c r="D32" t="str">
+        <f>C15</f>
+        <v>Spruce</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5">
+      <c r="B33" t="s">
+        <v>127</v>
+      </c>
+      <c r="C33" t="str">
+        <f t="shared" ref="C33:C34" si="0">$C$25</f>
+        <v>SPF</v>
+      </c>
+      <c r="D33" t="str">
+        <f>C16</f>
+        <v>Pine</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5">
+      <c r="B34" t="s">
+        <v>127</v>
+      </c>
+      <c r="C34" t="str">
+        <f t="shared" si="0"/>
+        <v>SPF</v>
+      </c>
+      <c r="D34" t="str">
+        <f>C17</f>
+        <v>Fir</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5">
+      <c r="B36" t="s">
+        <v>127</v>
+      </c>
+      <c r="C36" t="str">
+        <f>C26</f>
+        <v>Hardwood</v>
+      </c>
+      <c r="D36" t="str">
+        <f>C21</f>
+        <v>Aspen</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5">
+      <c r="B38" t="s">
+        <v>127</v>
+      </c>
+      <c r="C38" t="str">
+        <f>C27</f>
+        <v>Hem-Fir</v>
+      </c>
+      <c r="D38" t="str">
+        <f>C18</f>
+        <v>Hemlock</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5">
+      <c r="B40" t="s">
+        <v>127</v>
+      </c>
+      <c r="C40" t="str">
+        <f>$C$28</f>
+        <v>DFL</v>
+      </c>
+      <c r="D40" t="str">
+        <f>C19</f>
+        <v>Douglas-fir</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5">
+      <c r="B41" t="s">
+        <v>127</v>
+      </c>
+      <c r="C41" t="str">
+        <f>$C$28</f>
+        <v>DFL</v>
+      </c>
+      <c r="D41" t="str">
+        <f>C20</f>
+        <v>Larch</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" s="3" customFormat="1">
+      <c r="B43" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C43" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D43" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E43" s="3" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2912,7 +3152,7 @@
         <v>1725</v>
       </c>
       <c r="D2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E2">
         <v>998</v>
@@ -2931,7 +3171,7 @@
         <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="2:8" s="3" customFormat="1">
@@ -2953,7 +3193,7 @@
         <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D10" t="str">
         <f>C6</f>
